--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487056_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487056_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9356</v>
+        <v>1.4958</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6493</v>
+        <v>2.2095</v>
       </c>
       <c r="F2" t="n">
         <v>-0.7137</v>
@@ -610,10 +610,10 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5645</v>
+        <v>-0.0043</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6544</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U2" t="n">
         <v>0.08989999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2278</v>
+        <v>0.1175</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3919</v>
+        <v>-0.5095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6198</v>
+        <v>0.627</v>
       </c>
       <c r="G3" t="n">
-        <v>1.489</v>
+        <v>-0.3734</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9842</v>
+        <v>-0.3962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5048</v>
+        <v>0.0228</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7964</v>
+        <v>0.3077</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5522</v>
+        <v>0.1449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2442</v>
+        <v>0.1628</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3074</v>
+        <v>-0.6811</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5411</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2606</v>
+        <v>-0.14</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3827</v>
+        <v>-0.3969</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3979</v>
+        <v>-0.1609</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0152</v>
+        <v>-0.236</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0649</v>
+        <v>-0.6562</v>
       </c>
       <c r="W3" t="n">
         <v>-0.6562</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0213</v>
+        <v>0.059</v>
       </c>
       <c r="E4" t="n">
         <v>0.6994</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7207</v>
+        <v>-0.6404</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3808</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0159</v>
+        <v>-0.9356</v>
       </c>
       <c r="T4" t="n">
         <v>-0.5076000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5083</v>
+        <v>-0.428</v>
       </c>
       <c r="V4" t="n">
         <v>1.7614</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2959</v>
+        <v>-0.3998</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8694</v>
+        <v>-0.9928</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5734</v>
+        <v>0.593</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3734</v>
+        <v>1.489</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3962</v>
+        <v>0.9842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0228</v>
+        <v>0.5048</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3077</v>
+        <v>1.7964</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1449</v>
+        <v>1.5522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1628</v>
+        <v>0.2442</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6811</v>
+        <v>-0.3074</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5411</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.14</v>
+        <v>0.2606</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5441</v>
+        <v>-0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8104</v>
+        <v>-0.2449</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5208</v>
+        <v>-0.2029</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2895</v>
+        <v>-0.042</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6562</v>
+        <v>-1.0649</v>
       </c>
       <c r="W5" t="n">
         <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9897</v>
+        <v>-0.6108</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7148</v>
+        <v>-1.8596</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7045</v>
+        <v>1.2488</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4285</v>
+        <v>-0.0201</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1632</v>
+        <v>-1.5338</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2652</v>
+        <v>1.5137</v>
       </c>
       <c r="J6" t="n">
-        <v>0.115</v>
+        <v>-0.3202</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6933</v>
+        <v>-1.5734</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5783</v>
+        <v>1.2531</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5435</v>
+        <v>0.3002</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8566</v>
+        <v>0.0396</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6869</v>
+        <v>0.2606</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7371</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.5744</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.6656</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1228</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.9301</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.6544</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.7403</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.1631</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.5138</v>
-      </c>
       <c r="X6" t="n">
-        <v>-1.3508</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2014</v>
+        <v>-1.3903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1839</v>
+        <v>1.3142</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3853</v>
+        <v>-2.7045</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4927</v>
+        <v>-2.4285</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3414</v>
+        <v>-1.1632</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1514</v>
+        <v>-1.2652</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0169</v>
+        <v>0.115</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3262</v>
+        <v>0.6933</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3431</v>
+        <v>-0.5783</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5096</v>
+        <v>-2.5435</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0152</v>
+        <v>-1.8566</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4944</v>
+        <v>-0.6869</v>
       </c>
       <c r="P7" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3034</v>
+        <v>-1.0549</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5024</v>
+        <v>-0.3146</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8058</v>
+        <v>-0.7403</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3704</v>
+        <v>0.1631</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3704</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5864</v>
+        <v>-1.83</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4605</v>
+        <v>-0.2573</v>
       </c>
       <c r="F8" t="n">
-        <v>0.874</v>
+        <v>-1.5727</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0201</v>
+        <v>-1.4927</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5338</v>
+        <v>-1.3414</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5137</v>
+        <v>-0.1514</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3202</v>
+        <v>1.0169</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5734</v>
+        <v>-0.3262</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2531</v>
+        <v>1.3431</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3002</v>
+        <v>-2.5096</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0396</v>
+        <v>-1.0152</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2606</v>
+        <v>-1.4944</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.2156</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1752</v>
+        <v>0.0612</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0404</v>
+        <v>-0.9932</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1228</v>
+        <v>-0.3704</v>
       </c>
       <c r="W8" t="n">
+        <v>-0.3704</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.1228</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3825</v>
+        <v>-3.3369</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0621</v>
+        <v>-0.8023</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3204</v>
+        <v>-2.5346</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6012</v>
@@ -1156,13 +1156,13 @@
         <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9287</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5221</v>
+        <v>-0.2624</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4521</v>
+        <v>-0.6663</v>
       </c>
       <c r="V9" t="n">
         <v>0.614</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0293</v>
+        <v>-4.1503</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9274</v>
+        <v>-1.968</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.102</v>
+        <v>-2.1823</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6688</v>
@@ -1234,13 +1234,13 @@
         <v>2.5091</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.4888</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3034</v>
+        <v>-0.3837</v>
       </c>
       <c r="V10" t="n">
         <v>0.7771</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.3431</v>
+        <v>-10.0458</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4639</v>
+        <v>-2.1664</v>
       </c>
       <c r="F11" t="n">
         <v>-7.8794</v>
@@ -1312,13 +1312,13 @@
         <v>16.4059</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.907299999999999</v>
+        <v>-6.6098</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8419</v>
+        <v>-2.5446</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.0651</v>
+        <v>-4.0652</v>
       </c>
       <c r="V11" t="n">
         <v>1.4294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9214</v>
+        <v>6.874</v>
       </c>
       <c r="E12" t="n">
-        <v>6.357</v>
+        <v>4.8549</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5644</v>
+        <v>2.0192</v>
       </c>
       <c r="G12" t="n">
         <v>6.5818</v>
@@ -1390,13 +1390,13 @@
         <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5435</v>
+        <v>1.4961</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4457</v>
+        <v>0.9436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0978</v>
+        <v>0.5525</v>
       </c>
       <c r="V12" t="n">
         <v>1.8842</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1035</v>
+        <v>3.1164</v>
       </c>
       <c r="E13" t="n">
-        <v>2.183</v>
+        <v>2.3833</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9205</v>
+        <v>0.7332</v>
       </c>
       <c r="G13" t="n">
         <v>3.3565</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5889</v>
+        <v>0.6018</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1057</v>
+        <v>0.0945</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6947</v>
+        <v>0.5073</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0147</v>
+        <v>2.5677</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6761</v>
+        <v>0.4897</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3386</v>
+        <v>2.078</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7138</v>
+        <v>1.6313</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6125</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3263</v>
+        <v>0.8354</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9603</v>
+        <v>2.0378</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5058</v>
+        <v>1.4437</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5455</v>
+        <v>0.5941</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6741</v>
+        <v>-0.4065</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1067</v>
+        <v>-0.6478</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7808</v>
+        <v>0.2413</v>
       </c>
       <c r="P14" t="n">
-        <v>0.965</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.193</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5355</v>
+        <v>1.2103</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6808</v>
+        <v>0.7331</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8546</v>
+        <v>0.4772</v>
       </c>
       <c r="V14" t="n">
-        <v>1.228</v>
+        <v>1.2702</v>
       </c>
       <c r="W14" t="n">
-        <v>1.228</v>
+        <v>0.614</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0739</v>
+        <v>2.2995</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1111</v>
+        <v>2.1754</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1851</v>
+        <v>0.1241</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6313</v>
+        <v>-0.7138</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7959000000000001</v>
+        <v>1.6125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8354</v>
+        <v>-2.3263</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0378</v>
+        <v>0.9603</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4437</v>
+        <v>1.5058</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5941</v>
+        <v>-0.5455</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4065</v>
+        <v>-1.6741</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6478</v>
+        <v>0.1067</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2413</v>
+        <v>-1.7808</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7165</v>
+        <v>0.8203</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1322</v>
+        <v>0.1801</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5843</v>
+        <v>0.6401</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2702</v>
+        <v>1.228</v>
       </c>
       <c r="W15" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2799</v>
+        <v>0.1973</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2876</v>
+        <v>0.5334</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5676</v>
+        <v>-0.3361</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1943</v>
+        <v>1.6659</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6323</v>
+        <v>0.5941</v>
       </c>
       <c r="I16" t="n">
-        <v>1.438</v>
+        <v>1.0717</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7889</v>
+        <v>2.0047</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.911</v>
+        <v>0.621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>1.3838</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5946</v>
+        <v>-0.3389</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.0268</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3159</v>
+        <v>-0.3121</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.772</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-2.1231</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-3.0881</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6552</v>
+        <v>0.8173</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0755</v>
+        <v>0.6518</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5796</v>
+        <v>0.1656</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>-1.5138</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5717</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5242</v>
+        <v>0.0842</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1328</v>
+        <v>-1.1889</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.657</v>
+        <v>1.2731</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6659</v>
+        <v>-0.1943</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5941</v>
+        <v>-1.6323</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0717</v>
+        <v>1.438</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0047</v>
+        <v>-0.7889</v>
       </c>
       <c r="K17" t="n">
-        <v>0.621</v>
+        <v>-0.911</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3838</v>
+        <v>0.1221</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3389</v>
+        <v>0.5946</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0268</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3121</v>
+        <v>1.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1231</v>
+        <v>-3.0881</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0958</v>
+        <v>1.4595</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2512</v>
+        <v>1.1743</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1554</v>
+        <v>0.2852</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5138</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5138</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0721</v>
+        <v>-0.2842</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7156</v>
+        <v>-1.1148</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6435</v>
+        <v>0.8305</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2311</v>
@@ -1858,13 +1858,13 @@
         <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5129</v>
+        <v>0.275</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8328</v>
+        <v>-0.232</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3199</v>
+        <v>0.507</v>
       </c>
       <c r="V18" t="n">
         <v>0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4243</v>
+        <v>-1.7362</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3246</v>
+        <v>0.1761</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0997</v>
+        <v>-1.9123</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2039</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7066</v>
+        <v>-0.0185</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5949</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1117</v>
+        <v>0.0757</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0297</v>
+        <v>-2.108</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0306</v>
+        <v>-0.4298</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9991</v>
+        <v>-1.6782</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2371</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0086</v>
+        <v>0.9132</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0132</v>
+        <v>0.6141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0218</v>
+        <v>0.2991</v>
       </c>
       <c r="V20" t="n">
         <v>-2.784</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>10.3431</v>
+        <v>11.0107</v>
       </c>
       <c r="E21" t="n">
-        <v>7.879399999999999</v>
+        <v>7.879299999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.463899999999999</v>
+        <v>3.1315</v>
       </c>
       <c r="G21" t="n">
         <v>10.6553</v>
@@ -2092,13 +2092,13 @@
         <v>10.6155</v>
       </c>
       <c r="S21" t="n">
-        <v>6.907299999999998</v>
+        <v>7.574999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>4.0652</v>
+        <v>4.0653</v>
       </c>
       <c r="U21" t="n">
-        <v>2.842</v>
+        <v>3.5097</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4292</v>
